--- a/Codelist Excel Files and Conversion Templates to XML/sampleMatrix.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/sampleMatrix.xlsx
@@ -985,7 +985,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Codes classifying the material class of a sample, planned or realized - soil, rock, grout, and so on. Used for the value of diggs:TargetSampleType/sampleMatrix (planned) and diggs:SampleType/sampleMatrix (as-built) so design and as-built share one vocabulary for the same concept. The soil/rock distinction matters at planning time even where the eventual matrix is uncertain: a design targeting a not-yet-drilled location may know only that the recovered material will be one or the other.</t>
+          <t>Codes classifying the material class of a sample, planned or realized - soil, rock, grout, and so on. Used for the value of diggs:DesignSampleType/sampleMatrix (planned) and diggs:SampleType/sampleMatrix (as-built) so design and as-built share one vocabulary for the same concept. The soil/rock distinction matters at planning time even where the eventual matrix is uncertain: a design targeting a not-yet-drilled location may know only that the recovered material will be one or the other.</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>//diggs:TargetSample/diggs:sampleMatrix</t>
+          <t>//diggs:DesignSample/diggs:sampleMatrix</t>
         </is>
       </c>
     </row>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>//diggs:TargetSample/diggs:sampleMatrix</t>
+          <t>//diggs:DesignSample/diggs:sampleMatrix</t>
         </is>
       </c>
     </row>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>//diggs:TargetSample/diggs:sampleMatrix</t>
+          <t>//diggs:DesignSample/diggs:sampleMatrix</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>//diggs:TargetSample/diggs:sampleMatrix</t>
+          <t>//diggs:DesignSample/diggs:sampleMatrix</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>//diggs:TargetSample/diggs:sampleMatrix</t>
+          <t>//diggs:DesignSample/diggs:sampleMatrix</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>//diggs:TargetSample/diggs:sampleMatrix</t>
+          <t>//diggs:DesignSample/diggs:sampleMatrix</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>//diggs:TargetSample/diggs:sampleMatrix</t>
+          <t>//diggs:DesignSample/diggs:sampleMatrix</t>
         </is>
       </c>
     </row>
